--- a/testing/Part1_TestingInputs.xlsx
+++ b/testing/Part1_TestingInputs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AS\PM\Projects\GradProject_Blinkit_P1\testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE259AA5-F654-4A57-B688-35D0490C26A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2C85FBD-08F8-4BAF-9A3A-23F773CA1F2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -176,15 +176,27 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -192,17 +204,50 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -518,444 +563,444 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
+      <c r="A4" s="5">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="D4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="1" t="s">
+      <c r="D5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
+      <c r="A6" s="5">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
+      <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
+      <c r="A8" s="5">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
+      <c r="A9" s="5">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" s="1" t="s">
+      <c r="D9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
+      <c r="A10" s="5">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1">
+      <c r="A11" s="5">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" s="1" t="s">
+      <c r="D11" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="1">
+      <c r="A12" s="5">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="1" t="s">
+      <c r="D12" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="1">
+      <c r="A13" s="5">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E13" s="1" t="s">
+      <c r="D13" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="1">
+      <c r="A14" s="5">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="1">
+      <c r="A15" s="5">
         <v>14</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="1">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="s">
+      <c r="A16" s="5">
+        <v>15</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E16" s="1" t="s">
+      <c r="D16" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="1">
+      <c r="A17" s="5">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="1">
+      <c r="A18" s="5">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E18" s="1" t="s">
+      <c r="D18" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="1">
+      <c r="A19" s="5">
         <v>18</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E19" s="1" t="s">
+      <c r="D19" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="1">
+      <c r="A20" s="5">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E20" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="1">
+      <c r="A21" s="5">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E21" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="1">
+      <c r="A22" s="5">
         <v>21</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="1">
+      <c r="A23" s="5">
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E23" s="1" t="s">
+      <c r="D23" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="1">
+      <c r="A24" s="5">
         <v>23</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="E24" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A25" s="1">
+      <c r="A25" s="5">
         <v>24</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E25" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="1">
+      <c r="A26" s="5">
         <v>25</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E26" s="1" t="s">
+      <c r="D26" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" s="5" t="s">
         <v>12</v>
       </c>
     </row>
